--- a/crates/xlstream-eval/tests/fixtures/issues/issue-76-self-referential-formulas.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/issues/issue-76-self-referential-formulas.xlsx
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
